--- a/survey_templates/042_healthcare_disparities_registration--survey_templates.xlsx
+++ b/survey_templates/042_healthcare_disparities_registration--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C91"/>
+  <dimension ref="A1:C89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'in-person'}</t>
+          <t>in-person</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'In-Person'}</t>
+          <t>In-Person</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'primary_care'}</t>
+          <t>primary_care</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Primary Care'}</t>
+          <t>Primary Care</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'social_worker'}</t>
+          <t>social_worker</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Social Worker'}</t>
+          <t>Social Worker</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'case_manager'}</t>
+          <t>case_manager</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Case Manager'}</t>
+          <t>Case Manager</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'clinic_manager'}</t>
+          <t>clinic_manager</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Clinic Manager'}</t>
+          <t>Clinic Manager</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'alabama'}</t>
+          <t>alabama</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Alabama'}</t>
+          <t>Alabama</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'alaska'}</t>
+          <t>alaska</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Alaska'}</t>
+          <t>Alaska</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'american_samoa'}</t>
+          <t>american_samoa</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'American Samoa'}</t>
+          <t>American Samoa</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'arizona'}</t>
+          <t>arizona</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Arizona'}</t>
+          <t>Arizona</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'arkansas'}</t>
+          <t>arkansas</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Arkansas'}</t>
+          <t>Arkansas</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'armed_forces_-_ae'}</t>
+          <t>armed_forces_-_ae</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Armed Forces - AE'}</t>
+          <t>Armed Forces - AE</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'armed_forces_-_ap'}</t>
+          <t>armed_forces_-_ap</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Armed Forces - AP'}</t>
+          <t>Armed Forces - AP</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'armed_forces_-_aa'}</t>
+          <t>armed_forces_-_aa</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Armed Forces - AA'}</t>
+          <t>Armed Forces - AA</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'california'}</t>
+          <t>california</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'California'}</t>
+          <t>California</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'colorado'}</t>
+          <t>colorado</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Colorado'}</t>
+          <t>Colorado</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'connecticut'}</t>
+          <t>connecticut</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Connecticut'}</t>
+          <t>Connecticut</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'delaware'}</t>
+          <t>delaware</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Delaware'}</t>
+          <t>Delaware</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'washington_d.c.'}</t>
+          <t>washington_d.c.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Washington D.C.'}</t>
+          <t>Washington D.C.</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'district_of_columbia'}</t>
+          <t>district_of_columbia</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'District of Columbia'}</t>
+          <t>District of Columbia</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'florida'}</t>
+          <t>florida</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Florida'}</t>
+          <t>Florida</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'georgia'}</t>
+          <t>georgia</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Georgia'}</t>
+          <t>Georgia</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'guam'}</t>
+          <t>guam</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Guam'}</t>
+          <t>Guam</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'hawaii'}</t>
+          <t>hawaii</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Hawaii'}</t>
+          <t>Hawaii</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'idaho'}</t>
+          <t>idaho</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Idaho'}</t>
+          <t>Idaho</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'illinois'}</t>
+          <t>illinois</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Illinois'}</t>
+          <t>Illinois</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'indiana'}</t>
+          <t>indiana</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Indiana'}</t>
+          <t>Indiana</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'iowa'}</t>
+          <t>iowa</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Iowa'}</t>
+          <t>Iowa</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'kansas'}</t>
+          <t>kansas</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Kansas'}</t>
+          <t>Kansas</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'kentucky'}</t>
+          <t>kentucky</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Kentucky'}</t>
+          <t>Kentucky</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'louisiana'}</t>
+          <t>louisiana</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Louisiana'}</t>
+          <t>Louisiana</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'maine'}</t>
+          <t>maine</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Maine'}</t>
+          <t>Maine</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'maryland'}</t>
+          <t>maryland</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Maryland'}</t>
+          <t>Maryland</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'massachusetts'}</t>
+          <t>massachusetts</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'Massachusetts'}</t>
+          <t>Massachusetts</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'michigan'}</t>
+          <t>michigan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'Michigan'}</t>
+          <t>Michigan</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'minnesota'}</t>
+          <t>minnesota</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'Minnesota'}</t>
+          <t>Minnesota</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'mississippi'}</t>
+          <t>mississippi</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'Mississippi'}</t>
+          <t>Mississippi</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'missouri'}</t>
+          <t>missouri</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'Missouri'}</t>
+          <t>Missouri</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_'montana'}</t>
+          <t>montana</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': 'Montana'}</t>
+          <t>Montana</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'label':_'nebraska'}</t>
+          <t>nebraska</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'label': 'Nebraska'}</t>
+          <t>Nebraska</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'label':_'nevada'}</t>
+          <t>nevada</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'label': 'Nevada'}</t>
+          <t>Nevada</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'label':_'new_hampshire'}</t>
+          <t>new_hampshire</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'label': 'New Hampshire'}</t>
+          <t>New Hampshire</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'label':_'new_jersey'}</t>
+          <t>new_jersey</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'label': 'New Jersey'}</t>
+          <t>New Jersey</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'label':_'new_york'}</t>
+          <t>new_york</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'label': 'New York'}</t>
+          <t>New York</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'label':_'north_carolina'}</t>
+          <t>north_carolina</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'label': 'North Carolina'}</t>
+          <t>North Carolina</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'label':_'north_dakota'}</t>
+          <t>north_dakota</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'label': 'North Dakota'}</t>
+          <t>North Dakota</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'label':_'northern_mariana_islands'}</t>
+          <t>northern_mariana_islands</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'label': 'Northern Mariana Islands'}</t>
+          <t>Northern Mariana Islands</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'label':_'ohio'}</t>
+          <t>ohio</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'label': 'Ohio'}</t>
+          <t>Ohio</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'label':_'oklahoma'}</t>
+          <t>oklahoma</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'label': 'Oklahoma'}</t>
+          <t>Oklahoma</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'label':_'oregon'}</t>
+          <t>oregon</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'label': 'Oregon'}</t>
+          <t>Oregon</t>
         </is>
       </c>
     </row>
@@ -1998,12 +1998,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'label':_'pennsylvania'}</t>
+          <t>pennsylvania</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'label': 'Pennsylvania'}</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
     </row>
@@ -2015,12 +2015,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'label':_'puerto_rico'}</t>
+          <t>puerto_rico</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'label': 'Puerto Rico'}</t>
+          <t>Puerto Rico</t>
         </is>
       </c>
     </row>
@@ -2032,12 +2032,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'label':_'rhode_island'}</t>
+          <t>rhode_island</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'label': 'Rhode Island'}</t>
+          <t>Rhode Island</t>
         </is>
       </c>
     </row>
@@ -2049,12 +2049,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'label':_'south_carolina'}</t>
+          <t>south_carolina</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'label': 'South Carolina'}</t>
+          <t>South Carolina</t>
         </is>
       </c>
     </row>
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'label':_'south_dakota'}</t>
+          <t>south_dakota</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'label': 'South Dakota'}</t>
+          <t>South Dakota</t>
         </is>
       </c>
     </row>
@@ -2083,12 +2083,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'label':_'tennessee'}</t>
+          <t>tennessee</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'label': 'Tennessee'}</t>
+          <t>Tennessee</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'label':_'texas'}</t>
+          <t>texas</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'label': 'Texas'}</t>
+          <t>Texas</t>
         </is>
       </c>
     </row>
@@ -2117,12 +2117,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'label':_'utah'}</t>
+          <t>utah</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'label': 'Utah'}</t>
+          <t>Utah</t>
         </is>
       </c>
     </row>
@@ -2134,12 +2134,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'label':_'vermont'}</t>
+          <t>vermont</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'label': 'Vermont'}</t>
+          <t>Vermont</t>
         </is>
       </c>
     </row>
@@ -2151,12 +2151,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'label':_'virgin_islands'}</t>
+          <t>virgin_islands</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'label': 'Virgin Islands'}</t>
+          <t>Virgin Islands</t>
         </is>
       </c>
     </row>
@@ -2168,12 +2168,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{'label':_'virginia'}</t>
+          <t>virginia</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'label': 'Virginia'}</t>
+          <t>Virginia</t>
         </is>
       </c>
     </row>
@@ -2185,12 +2185,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{'label':_'washington'}</t>
+          <t>washington</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{'label': 'Washington'}</t>
+          <t>Washington</t>
         </is>
       </c>
     </row>
@@ -2202,12 +2202,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{'label':_'washington_d.c.'}</t>
+          <t>west_virginia</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{'label': 'Washington D.C.'}</t>
+          <t>West Virginia</t>
         </is>
       </c>
     </row>
@@ -2219,12 +2219,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{'label':_'west_virginia'}</t>
+          <t>wisconsin</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{'label': 'West Virginia'}</t>
+          <t>Wisconsin</t>
         </is>
       </c>
     </row>
@@ -2236,12 +2236,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>{'label':_'wisconsin'}</t>
+          <t>wyoming</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{'label': 'Wisconsin'}</t>
+          <t>Wyoming</t>
         </is>
       </c>
     </row>
@@ -2253,46 +2253,46 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>{'label':_'wyoming'}</t>
+          <t>us_virgin_islands</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>{'label': 'Wyoming'}</t>
+          <t>US Virgin Islands</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>state_choices</t>
+          <t>language_choices</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>{'label':_'puerto_rico'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>{'label': 'Puerto Rico'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>state_choices</t>
+          <t>language_choices</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>{'label':_'us_virgin_islands'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>{'label': 'US Virgin Islands'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -2304,46 +2304,46 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>{'label':_'english'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>{'label': 'English'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>language_choices</t>
+          <t>patient_gender_choices</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>{'label':_'spanish'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>{'label': 'Spanish'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>language_choices</t>
+          <t>patient_gender_choices</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -2355,80 +2355,80 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>{'label':_'male'}</t>
+          <t>non-binary</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>{'label': 'Male'}</t>
+          <t>Non-Binary</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>patient_gender_choices</t>
+          <t>patient_age_group_choices</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>{'label':_'female'}</t>
+          <t>18-64</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>{'label': 'Female'}</t>
+          <t>18-64</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>patient_gender_choices</t>
+          <t>patient_age_group_choices</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>{'label':_'non-binary'}</t>
+          <t>65_or_older</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>{'label': 'Non-Binary'}</t>
+          <t>65 or Older</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>patient_age_group_choices</t>
+          <t>patient_race_choices</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>{'label':_'18-64'}</t>
+          <t>asian</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>{'label': '18-64'}</t>
+          <t>Asian</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>patient_age_group_choices</t>
+          <t>patient_race_choices</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>{'label':_'65_or_older'}</t>
+          <t>black_or_african_american</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>{'label': '65 or Older'}</t>
+          <t>Black or African American</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>{'label':_'asian'}</t>
+          <t>native_american</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>{'label': 'Asian'}</t>
+          <t>Native American</t>
         </is>
       </c>
     </row>
@@ -2457,12 +2457,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>{'label':_'black_or_african_american'}</t>
+          <t>pacific_islander</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>{'label': 'Black or African American'}</t>
+          <t>Pacific Islander</t>
         </is>
       </c>
     </row>
@@ -2474,12 +2474,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>{'label':_'native_american'}</t>
+          <t>white</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>{'label': 'Native American'}</t>
+          <t>White</t>
         </is>
       </c>
     </row>
@@ -2491,46 +2491,46 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>{'label':_'pacific_islander'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>{'label': 'Pacific Islander'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>patient_race_choices</t>
+          <t>patient_ethnicity_choices</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>{'label':_'white'}</t>
+          <t>asian</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>{'label': 'White'}</t>
+          <t>Asian</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>patient_race_choices</t>
+          <t>patient_ethnicity_choices</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>black_or_african_american</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Black or African American</t>
         </is>
       </c>
     </row>
@@ -2542,12 +2542,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>{'label':_'asian'}</t>
+          <t>native_american</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>{'label': 'Asian'}</t>
+          <t>Native American</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>{'label':_'black_or_african_american'}</t>
+          <t>pacific_islander</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>{'label': 'Black or African American'}</t>
+          <t>Pacific Islander</t>
         </is>
       </c>
     </row>
@@ -2576,12 +2576,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>{'label':_'native_american'}</t>
+          <t>white</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>{'label': 'Native American'}</t>
+          <t>White</t>
         </is>
       </c>
     </row>
@@ -2593,12 +2593,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>{'label':_'pacific_islander'}</t>
+          <t>hispanic_or_latino</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>{'label': 'Pacific Islander'}</t>
+          <t>Hispanic or Latino</t>
         </is>
       </c>
     </row>
@@ -2610,46 +2610,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>{'label':_'white'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>{'label': 'White'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>patient_ethnicity_choices</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>{'label':_'hispanic_or_latino'}</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>{'label': 'Hispanic or Latino'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>patient_ethnicity_choices</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>{'label':_'other'}</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
